--- a/alk-api/resources/xlsx/For ERP-1.xlsx
+++ b/alk-api/resources/xlsx/For ERP-1.xlsx
@@ -556,7 +556,7 @@
         <v>FROZEN FRESHWATER SHRIMP</v>
       </c>
       <c r="D11" t="str">
-        <v>COOKED PEELED &amp; DEVEINED TAIL OFF / TAIL-OFF</v>
+        <v>WHOLE ROUND</v>
       </c>
       <c r="F11" t="str">
         <v>1 x 1 BAG</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FROZEN VANNAMEI SHRIMP 2ND GRADE</v>
+        <v>FROZEN VANNAMEI WHITE SHRIMP</v>
       </c>
       <c r="D33" t="str">
         <v>RAW PEELED &amp; DEVEINED / UNDEVEINED TAIL OFF</v>
@@ -848,7 +848,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FROZEN VANNAMEI WHITE SHRIMP</v>
+        <v>FROZEN YELLOWFIN TUNA</v>
       </c>
       <c r="D34" t="str">
         <v>RAW PEELED &amp; DEVEINED T/OFF BUTTERFLY</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FROZEN YELLOWFIN TUNA</v>
+        <v/>
       </c>
       <c r="D35" t="str">
         <v>RAW PEELED &amp; DEVEINED T/ON BUTTERFLY</v>
